--- a/IDEB_Municipios2025.xlsx
+++ b/IDEB_Municipios2025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,11 +626,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>293.44</v>
+        <v>257.29</v>
       </c>
       <c r="F5" t="n">
         <v>277.56</v>
@@ -639,7 +639,7 @@
         <v>291.21</v>
       </c>
       <c r="H5" t="n">
-        <v>266.9</v>
+        <v>237.24</v>
       </c>
       <c r="I5" t="n">
         <v>269.54</v>
@@ -648,13 +648,13 @@
         <v>279.9</v>
       </c>
       <c r="K5" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="6">
@@ -671,24 +671,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>245.55</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>293.44</v>
+      </c>
+      <c r="F6" t="n">
+        <v>277.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>291.21</v>
+      </c>
       <c r="H6" t="n">
-        <v>227.61</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>266.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>269.54</v>
+      </c>
+      <c r="J6" t="n">
+        <v>279.9</v>
+      </c>
       <c r="K6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -704,36 +716,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>257.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>277.56</v>
-      </c>
-      <c r="G7" t="n">
-        <v>291.21</v>
-      </c>
+        <v>245.55</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>237.24</v>
-      </c>
-      <c r="I7" t="n">
-        <v>269.54</v>
-      </c>
-      <c r="J7" t="n">
-        <v>279.9</v>
-      </c>
+        <v>227.61</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.9</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -836,33 +836,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>295.73</v>
       </c>
       <c r="G10" t="n">
         <v>300.53</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>298.97</v>
       </c>
       <c r="J10" t="n">
         <v>292.88</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>6.4</v>
       </c>
@@ -935,29 +923,17 @@
       <c r="E12" t="n">
         <v>273.87</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>259.84</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>7.7</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1052,30 +1028,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>253.49</v>
       </c>
       <c r="F15" t="n">
-        <v>289.34</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>286.19</v>
+      </c>
+      <c r="G15" t="n">
+        <v>296.12</v>
+      </c>
       <c r="H15" t="n">
         <v>235.66</v>
       </c>
       <c r="I15" t="n">
-        <v>281.8</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>280.71</v>
+      </c>
+      <c r="J15" t="n">
+        <v>288.43</v>
+      </c>
       <c r="K15" t="n">
         <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1091,36 +1073,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>253.49</v>
       </c>
       <c r="F16" t="n">
-        <v>286.19</v>
-      </c>
-      <c r="G16" t="n">
-        <v>296.12</v>
-      </c>
+        <v>289.34</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>235.66</v>
       </c>
       <c r="I16" t="n">
-        <v>280.71</v>
-      </c>
-      <c r="J16" t="n">
-        <v>288.43</v>
-      </c>
+        <v>281.8</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1259,30 +1235,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>232.41</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>257.59</v>
+        <v>253.48</v>
       </c>
       <c r="G20" t="n">
         <v>278.77</v>
       </c>
-      <c r="H20" t="n">
-        <v>219.59</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>259.72</v>
+        <v>253.2</v>
       </c>
       <c r="J20" t="n">
         <v>283.65</v>
       </c>
-      <c r="K20" t="n">
-        <v>6.3</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>5.1</v>
       </c>
@@ -1343,35 +1313,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>232.41</v>
       </c>
       <c r="F22" t="n">
-        <v>253.48</v>
+        <v>257.59</v>
       </c>
       <c r="G22" t="n">
         <v>278.77</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" t="n">
+        <v>219.59</v>
       </c>
       <c r="I22" t="n">
-        <v>253.2</v>
+        <v>259.72</v>
       </c>
       <c r="J22" t="n">
         <v>283.65</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K22" t="n">
+        <v>6.3</v>
       </c>
       <c r="L22" t="n">
         <v>5.1</v>
@@ -1398,29 +1362,17 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>301.91</v>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>287.27</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>5.2</v>
       </c>
@@ -1526,33 +1478,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
         <v>270.43</v>
       </c>
       <c r="G26" t="n">
         <v>285.3</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>272.47</v>
       </c>
       <c r="J26" t="n">
         <v>281.07</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>5.7</v>
       </c>
@@ -1712,33 +1652,21 @@
       <c r="F30" t="n">
         <v>271.59</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>239.79</v>
       </c>
       <c r="I30" t="n">
         <v>262.65</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>7.2</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1931,33 +1859,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
         <v>245.09</v>
       </c>
       <c r="G35" t="n">
         <v>269.45</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>253.42</v>
       </c>
       <c r="J35" t="n">
         <v>259.44</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>5</v>
       </c>
@@ -1985,29 +1901,17 @@
       <c r="E36" t="n">
         <v>250.05</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>234.04</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>7</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2072,33 +1976,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
         <v>275.55</v>
       </c>
       <c r="G38" t="n">
         <v>291.07</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>276.58</v>
       </c>
       <c r="J38" t="n">
         <v>290.12</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>5.8</v>
       </c>
@@ -2126,29 +2018,17 @@
       <c r="E39" t="n">
         <v>252.84</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>230.23</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
         <v>6.8</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2210,41 +2090,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>233.9</v>
       </c>
       <c r="F41" t="n">
-        <v>271.56</v>
+        <v>263.05</v>
       </c>
       <c r="G41" t="n">
-        <v>296.97</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>303.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>223.85</v>
       </c>
       <c r="I41" t="n">
-        <v>268.04</v>
+        <v>263.34</v>
       </c>
       <c r="J41" t="n">
-        <v>291.41</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>296.16</v>
+      </c>
+      <c r="K41" t="n">
+        <v>6.3</v>
       </c>
       <c r="L41" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="M41" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="42">
@@ -2261,30 +2135,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>233.9</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>260.03</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
-        <v>223.85</v>
-      </c>
+        <v>271.56</v>
+      </c>
+      <c r="G42" t="n">
+        <v>296.97</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>261.67</v>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>6.3</v>
-      </c>
+        <v>268.04</v>
+      </c>
+      <c r="J42" t="n">
+        <v>291.41</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>5</v>
-      </c>
-      <c r="M42" t="inlineStr"/>
+        <v>5.6</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2300,36 +2174,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>233.9</v>
       </c>
       <c r="F43" t="n">
-        <v>263.05</v>
-      </c>
-      <c r="G43" t="n">
-        <v>303.7</v>
-      </c>
+        <v>260.03</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>223.85</v>
       </c>
       <c r="I43" t="n">
-        <v>263.34</v>
-      </c>
-      <c r="J43" t="n">
-        <v>296.16</v>
-      </c>
+        <v>261.67</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>6.3</v>
       </c>
       <c r="L43" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5.4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2432,33 +2300,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
         <v>253.98</v>
       </c>
       <c r="G46" t="n">
         <v>277.57</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>258.03</v>
       </c>
       <c r="J46" t="n">
         <v>283.58</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>5.1</v>
       </c>
@@ -2483,33 +2339,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
         <v>276.29</v>
       </c>
       <c r="G47" t="n">
         <v>303.15</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>260.08</v>
       </c>
       <c r="J47" t="n">
         <v>286.68</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>5.6</v>
       </c>
@@ -2744,48 +2588,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>283.4</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>280.79</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>4.8</v>
-      </c>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>224.66</v>
+      </c>
+      <c r="F53" t="n">
+        <v>257.22</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>215.28</v>
+      </c>
+      <c r="I53" t="n">
+        <v>257.99</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2801,30 +2627,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>224.66</v>
-      </c>
-      <c r="F54" t="n">
-        <v>257.22</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>215.28</v>
-      </c>
-      <c r="I54" t="n">
-        <v>257.99</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="n">
-        <v>6</v>
-      </c>
-      <c r="L54" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>280.79</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2885,30 +2705,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
-        <v>272.21</v>
-      </c>
-      <c r="G56" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="n">
-        <v>272.89</v>
-      </c>
-      <c r="J56" t="n">
-        <v>290.11</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M56" t="n">
-        <v>5.1</v>
-      </c>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>227.78</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>217.17</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2924,36 +2738,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>227.78</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>217.17</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>272.21</v>
+      </c>
+      <c r="G57" t="n">
+        <v>294.9</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>272.89</v>
+      </c>
+      <c r="J57" t="n">
+        <v>290.11</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3014,36 +2822,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>235.72</v>
       </c>
-      <c r="F59" t="n">
-        <v>281.53</v>
-      </c>
-      <c r="G59" t="n">
-        <v>281.77</v>
-      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>218.06</v>
       </c>
-      <c r="I59" t="n">
-        <v>271.82</v>
-      </c>
-      <c r="J59" t="n">
-        <v>278.7</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>6.4</v>
       </c>
-      <c r="L59" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M59" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3059,36 +2855,36 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>235.72</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="G60" t="n">
+        <v>281.77</v>
+      </c>
       <c r="H60" t="n">
         <v>218.06</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>271.82</v>
+      </c>
+      <c r="J60" t="n">
+        <v>278.7</v>
+      </c>
       <c r="K60" t="n">
         <v>6.4</v>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3107,33 +2903,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
         <v>281.53</v>
       </c>
       <c r="G61" t="n">
         <v>281.77</v>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>271.82</v>
       </c>
       <c r="J61" t="n">
         <v>278.7</v>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>5.8</v>
       </c>
@@ -3287,33 +3071,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>282.85</v>
       </c>
       <c r="G65" t="n">
         <v>302.91</v>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>272.78</v>
       </c>
       <c r="J65" t="n">
         <v>293.99</v>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
         <v>5.9</v>
       </c>
@@ -3341,29 +3113,17 @@
       <c r="E66" t="n">
         <v>244.1</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>231.51</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
         <v>6.8</v>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -3476,29 +3236,17 @@
       <c r="E69" t="n">
         <v>245.22</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>232.65</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
         <v>6.9</v>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -3552,49 +3300,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fundão</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>3202207</v>
-      </c>
+          <t>Estado do Espírito Santo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" t="n">
+        <v>242.15</v>
       </c>
       <c r="F71" t="n">
-        <v>284.73</v>
+        <v>266.28</v>
       </c>
       <c r="G71" t="n">
-        <v>282.11</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>283.76</v>
+      </c>
+      <c r="H71" t="n">
+        <v>232.76</v>
       </c>
       <c r="I71" t="n">
-        <v>268.66</v>
+        <v>265.76</v>
       </c>
       <c r="J71" t="n">
-        <v>283.42</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>283.47</v>
+      </c>
+      <c r="K71" t="n">
+        <v>6.8</v>
       </c>
       <c r="L71" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="M71" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="72">
@@ -3603,36 +3343,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fundão</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>3202207</v>
-      </c>
+          <t>Estado do Espírito Santo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>235.49</v>
+        <v>234.18</v>
       </c>
       <c r="F72" t="n">
-        <v>252.67</v>
+        <v>262.52</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>225.85</v>
+        <v>222.83</v>
       </c>
       <c r="I72" t="n">
-        <v>254.6</v>
+        <v>262.87</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="L72" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="M72" t="inlineStr"/>
     </row>
@@ -3687,44 +3425,38 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Governador Lindenberg</t>
+          <t>Fundão</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3202256</v>
+        <v>3202207</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>250</v>
+        <v>235.49</v>
       </c>
       <c r="F74" t="n">
-        <v>268.35</v>
-      </c>
-      <c r="G74" t="n">
-        <v>295.78</v>
-      </c>
+        <v>252.67</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>233.87</v>
+        <v>225.85</v>
       </c>
       <c r="I74" t="n">
-        <v>266.77</v>
-      </c>
-      <c r="J74" t="n">
-        <v>290.73</v>
-      </c>
+        <v>254.6</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="L74" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M74" t="n">
-        <v>5.1</v>
-      </c>
+        <v>4.9</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3732,32 +3464,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Governador Lindenberg</t>
+          <t>Fundão</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3202256</v>
+        <v>3202207</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>250</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="n">
-        <v>233.87</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="n">
-        <v>7</v>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>284.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>282.11</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>268.66</v>
+      </c>
+      <c r="J75" t="n">
+        <v>283.42</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3773,42 +3511,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>268.35</v>
-      </c>
-      <c r="G76" t="n">
-        <v>295.78</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>266.77</v>
-      </c>
-      <c r="J76" t="n">
-        <v>290.73</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M76" t="n">
-        <v>5.1</v>
-      </c>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>250</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>233.87</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>7</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3816,49 +3536,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Guarapari</t>
+          <t>Governador Lindenberg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3202405</v>
+        <v>3202256</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>289.65</v>
+        <v>268.35</v>
       </c>
       <c r="G77" t="n">
-        <v>286.47</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>295.78</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>275.1</v>
+        <v>266.77</v>
       </c>
       <c r="J77" t="n">
-        <v>287.37</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>290.73</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="M77" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="78">
@@ -3867,38 +3575,44 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Guarapari</t>
+          <t>Governador Lindenberg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3202405</v>
+        <v>3202256</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229.17</v>
+        <v>250</v>
       </c>
       <c r="F78" t="n">
-        <v>259.52</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+        <v>268.35</v>
+      </c>
+      <c r="G78" t="n">
+        <v>295.78</v>
+      </c>
       <c r="H78" t="n">
-        <v>218.43</v>
+        <v>233.87</v>
       </c>
       <c r="I78" t="n">
-        <v>256.72</v>
-      </c>
-      <c r="J78" t="inlineStr"/>
+        <v>266.77</v>
+      </c>
+      <c r="J78" t="n">
+        <v>290.73</v>
+      </c>
       <c r="K78" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="L78" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M78" t="n">
         <v>5.1</v>
       </c>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3914,35 +3628,29 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>229.17</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>261.73</v>
+        <v>289.65</v>
       </c>
       <c r="G79" t="n">
         <v>286.47</v>
       </c>
-      <c r="H79" t="n">
-        <v>218.43</v>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>258.07</v>
+        <v>275.1</v>
       </c>
       <c r="J79" t="n">
         <v>287.37</v>
       </c>
-      <c r="K79" t="n">
-        <v>6.3</v>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="M79" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -3951,49 +3659,43 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Guaçuí</t>
+          <t>Guarapari</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3202306</v>
+        <v>3202405</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>229.17</v>
       </c>
       <c r="F80" t="n">
-        <v>253.43</v>
+        <v>261.73</v>
       </c>
       <c r="G80" t="n">
-        <v>295.54</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>286.47</v>
+      </c>
+      <c r="H80" t="n">
+        <v>218.43</v>
       </c>
       <c r="I80" t="n">
-        <v>256.1</v>
+        <v>258.07</v>
       </c>
       <c r="J80" t="n">
-        <v>285.26</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>287.37</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6.3</v>
       </c>
       <c r="L80" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M80" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="81">
@@ -4002,11 +3704,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Guaçuí</t>
+          <t>Guarapari</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3202306</v>
+        <v>3202405</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4014,24 +3716,24 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>238.01</v>
+        <v>229.17</v>
       </c>
       <c r="F81" t="n">
-        <v>262.89</v>
+        <v>259.52</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>224.52</v>
+        <v>218.43</v>
       </c>
       <c r="I81" t="n">
-        <v>263.85</v>
+        <v>256.72</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="L81" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M81" t="inlineStr"/>
     </row>
@@ -4049,32 +3751,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>238.01</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>261.37</v>
+        <v>253.43</v>
       </c>
       <c r="G82" t="n">
         <v>295.54</v>
       </c>
-      <c r="H82" t="n">
-        <v>224.52</v>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>262.61</v>
+        <v>256.1</v>
       </c>
       <c r="J82" t="n">
         <v>285.26</v>
       </c>
-      <c r="K82" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M82" t="n">
         <v>5.1</v>
@@ -4086,50 +3782,38 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ibatiba</t>
+          <t>Guaçuí</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3202454</v>
+        <v>3202306</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>238.01</v>
       </c>
       <c r="F83" t="n">
-        <v>282.55</v>
-      </c>
-      <c r="G83" t="n">
-        <v>289.54</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>262.89</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>224.52</v>
       </c>
       <c r="I83" t="n">
-        <v>279.05</v>
-      </c>
-      <c r="J83" t="n">
-        <v>288.07</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>263.85</v>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>6.5</v>
       </c>
       <c r="L83" t="n">
-        <v>6</v>
-      </c>
-      <c r="M83" t="n">
-        <v>4.9</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4137,38 +3821,44 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ibatiba</t>
+          <t>Guaçuí</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3202454</v>
+        <v>3202306</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>236.24</v>
+        <v>238.01</v>
       </c>
       <c r="F84" t="n">
-        <v>291.27</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>261.37</v>
+      </c>
+      <c r="G84" t="n">
+        <v>295.54</v>
+      </c>
       <c r="H84" t="n">
-        <v>224.36</v>
+        <v>224.52</v>
       </c>
       <c r="I84" t="n">
-        <v>289.65</v>
-      </c>
-      <c r="J84" t="inlineStr"/>
+        <v>262.61</v>
+      </c>
+      <c r="J84" t="n">
+        <v>285.26</v>
+      </c>
       <c r="K84" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="L84" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M84" t="n">
         <v>5.1</v>
       </c>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4184,35 +3874,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>236.24</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>287.6</v>
+        <v>282.55</v>
       </c>
       <c r="G85" t="n">
         <v>289.54</v>
       </c>
-      <c r="H85" t="n">
-        <v>224.36</v>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>285.19</v>
+        <v>279.05</v>
       </c>
       <c r="J85" t="n">
         <v>288.07</v>
       </c>
-      <c r="K85" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M85" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="86">
@@ -4221,50 +3905,38 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ibiraçu</t>
+          <t>Ibatiba</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3202504</v>
+        <v>3202454</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>236.24</v>
       </c>
       <c r="F86" t="n">
-        <v>260.86</v>
-      </c>
-      <c r="G86" t="n">
-        <v>271.26</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>291.27</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>224.36</v>
       </c>
       <c r="I86" t="n">
-        <v>255.66</v>
-      </c>
-      <c r="J86" t="n">
-        <v>286.3</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>289.65</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>6.4</v>
       </c>
       <c r="L86" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M86" t="n">
-        <v>4.8</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4272,44 +3944,44 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ibiraçu</t>
+          <t>Ibatiba</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3202504</v>
+        <v>3202454</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>245.46</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>236.24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>287.6</v>
+      </c>
+      <c r="G87" t="n">
+        <v>289.54</v>
+      </c>
       <c r="H87" t="n">
-        <v>228.81</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
+        <v>224.36</v>
+      </c>
+      <c r="I87" t="n">
+        <v>285.19</v>
+      </c>
+      <c r="J87" t="n">
+        <v>288.07</v>
+      </c>
       <c r="K87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="L87" t="n">
+        <v>5</v>
+      </c>
+      <c r="M87" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4325,30 +3997,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>245.46</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>260.86</v>
       </c>
       <c r="G88" t="n">
         <v>271.26</v>
       </c>
-      <c r="H88" t="n">
-        <v>228.81</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>255.66</v>
       </c>
       <c r="J88" t="n">
         <v>286.3</v>
       </c>
-      <c r="K88" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>5.2</v>
       </c>
@@ -4362,44 +4028,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ibitirama</t>
+          <t>Ibiraçu</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3202553</v>
+        <v>3202504</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>243.25</v>
-      </c>
-      <c r="F89" t="n">
-        <v>264.41</v>
-      </c>
-      <c r="G89" t="n">
-        <v>291.03</v>
-      </c>
+        <v>245.46</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>222.26</v>
-      </c>
-      <c r="I89" t="n">
-        <v>262.7</v>
-      </c>
-      <c r="J89" t="n">
-        <v>288.84</v>
-      </c>
+        <v>228.81</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L89" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M89" t="n">
-        <v>5</v>
-      </c>
+        <v>6.7</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4407,49 +4061,43 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ibitirama</t>
+          <t>Ibiraçu</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3202553</v>
+        <v>3202504</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>245.46</v>
       </c>
       <c r="F90" t="n">
-        <v>264.41</v>
+        <v>260.86</v>
       </c>
       <c r="G90" t="n">
-        <v>291.03</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>271.26</v>
+      </c>
+      <c r="H90" t="n">
+        <v>228.81</v>
       </c>
       <c r="I90" t="n">
-        <v>262.7</v>
+        <v>255.66</v>
       </c>
       <c r="J90" t="n">
-        <v>288.84</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>286.3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>6.7</v>
       </c>
       <c r="L90" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="91">
@@ -4472,29 +4120,17 @@
       <c r="E91" t="n">
         <v>243.25</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>222.26</v>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
         <v>6.4</v>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4503,49 +4139,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Iconha</t>
+          <t>Ibitirama</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3202603</v>
+        <v>3202553</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>292.41</v>
+        <v>264.41</v>
       </c>
       <c r="G92" t="n">
-        <v>304.51</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>291.03</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>286.94</v>
+        <v>262.7</v>
       </c>
       <c r="J92" t="n">
-        <v>297.38</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>288.84</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="M92" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -4554,38 +4178,44 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Iconha</t>
+          <t>Ibitirama</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3202603</v>
+        <v>3202553</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>244.82</v>
+        <v>243.25</v>
       </c>
       <c r="F93" t="n">
-        <v>284.12</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
+        <v>264.41</v>
+      </c>
+      <c r="G93" t="n">
+        <v>291.03</v>
+      </c>
       <c r="H93" t="n">
-        <v>231.54</v>
+        <v>222.26</v>
       </c>
       <c r="I93" t="n">
-        <v>275.92</v>
-      </c>
-      <c r="J93" t="inlineStr"/>
+        <v>262.7</v>
+      </c>
+      <c r="J93" t="n">
+        <v>288.84</v>
+      </c>
       <c r="K93" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L93" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M93" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="M93" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4601,32 +4231,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>244.82</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>290.34</v>
+        <v>292.41</v>
       </c>
       <c r="G94" t="n">
         <v>304.51</v>
       </c>
-      <c r="H94" t="n">
-        <v>231.54</v>
-      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>284.18</v>
+        <v>286.94</v>
       </c>
       <c r="J94" t="n">
         <v>297.38</v>
       </c>
-      <c r="K94" t="n">
-        <v>6.8</v>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M94" t="n">
         <v>5.3</v>
@@ -4638,50 +4262,38 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Irupi</t>
+          <t>Iconha</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3202652</v>
+        <v>3202603</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>244.82</v>
       </c>
       <c r="F95" t="n">
-        <v>283.27</v>
-      </c>
-      <c r="G95" t="n">
-        <v>294.84</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>284.12</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>231.54</v>
       </c>
       <c r="I95" t="n">
-        <v>284.15</v>
-      </c>
-      <c r="J95" t="n">
-        <v>278.39</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>275.92</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>6.8</v>
       </c>
       <c r="L95" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>5</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4689,38 +4301,44 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Irupi</t>
+          <t>Iconha</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3202652</v>
+        <v>3202603</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>239.27</v>
+        <v>244.82</v>
       </c>
       <c r="F96" t="n">
-        <v>260.36</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
+        <v>290.34</v>
+      </c>
+      <c r="G96" t="n">
+        <v>304.51</v>
+      </c>
       <c r="H96" t="n">
-        <v>219.29</v>
+        <v>231.54</v>
       </c>
       <c r="I96" t="n">
-        <v>256.26</v>
-      </c>
-      <c r="J96" t="inlineStr"/>
+        <v>284.18</v>
+      </c>
+      <c r="J96" t="n">
+        <v>297.38</v>
+      </c>
       <c r="K96" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="L96" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M96" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="M96" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4736,32 +4354,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>239.27</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>276.18</v>
+        <v>283.27</v>
       </c>
       <c r="G97" t="n">
         <v>294.84</v>
       </c>
-      <c r="H97" t="n">
-        <v>219.29</v>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>275.53</v>
+        <v>284.15</v>
       </c>
       <c r="J97" t="n">
         <v>278.39</v>
       </c>
-      <c r="K97" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="M97" t="n">
         <v>5</v>
@@ -4773,44 +4385,38 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Itaguaçu</t>
+          <t>Irupi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3202702</v>
+        <v>3202652</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>265.66</v>
+        <v>239.27</v>
       </c>
       <c r="F98" t="n">
-        <v>285.07</v>
-      </c>
-      <c r="G98" t="n">
-        <v>278.96</v>
-      </c>
+        <v>260.36</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>249.1</v>
+        <v>219.29</v>
       </c>
       <c r="I98" t="n">
-        <v>277.28</v>
-      </c>
-      <c r="J98" t="n">
-        <v>277.33</v>
-      </c>
+        <v>256.26</v>
+      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="L98" t="n">
-        <v>6</v>
-      </c>
-      <c r="M98" t="n">
-        <v>4.8</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4818,44 +4424,44 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Itaguaçu</t>
+          <t>Irupi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3202702</v>
+        <v>3202652</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>265.66</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+        <v>239.27</v>
+      </c>
+      <c r="F99" t="n">
+        <v>276.18</v>
+      </c>
+      <c r="G99" t="n">
+        <v>294.84</v>
+      </c>
       <c r="H99" t="n">
-        <v>249.1</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
+        <v>219.29</v>
+      </c>
+      <c r="I99" t="n">
+        <v>275.53</v>
+      </c>
+      <c r="J99" t="n">
+        <v>278.39</v>
+      </c>
       <c r="K99" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="L99" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M99" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4874,33 +4480,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
         <v>285.07</v>
       </c>
       <c r="G100" t="n">
         <v>278.96</v>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
         <v>277.28</v>
       </c>
       <c r="J100" t="n">
         <v>277.33</v>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
         <v>6</v>
       </c>
@@ -4914,50 +4508,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Itapemirim</t>
+          <t>Itaguaçu</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3202801</v>
+        <v>3202702</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>272.02</v>
-      </c>
-      <c r="G101" t="n">
-        <v>290.06</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>269.52</v>
-      </c>
-      <c r="J101" t="n">
-        <v>286.01</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M101" t="n">
-        <v>5</v>
-      </c>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>265.66</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>249.1</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4965,38 +4541,44 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Itapemirim</t>
+          <t>Itaguaçu</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3202801</v>
+        <v>3202702</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229.69</v>
+        <v>265.66</v>
       </c>
       <c r="F102" t="n">
-        <v>274.35</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
+        <v>285.07</v>
+      </c>
+      <c r="G102" t="n">
+        <v>278.96</v>
+      </c>
       <c r="H102" t="n">
-        <v>219.98</v>
+        <v>249.1</v>
       </c>
       <c r="I102" t="n">
-        <v>272.88</v>
-      </c>
-      <c r="J102" t="inlineStr"/>
+        <v>277.28</v>
+      </c>
+      <c r="J102" t="n">
+        <v>277.33</v>
+      </c>
       <c r="K102" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="L102" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M102" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M102" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5012,32 +4594,26 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>229.69</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
-        <v>273.46</v>
+        <v>272.02</v>
       </c>
       <c r="G103" t="n">
         <v>290.06</v>
       </c>
-      <c r="H103" t="n">
-        <v>219.98</v>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>271.61</v>
+        <v>269.52</v>
       </c>
       <c r="J103" t="n">
         <v>286.01</v>
       </c>
-      <c r="K103" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="M103" t="n">
         <v>5</v>
@@ -5049,50 +4625,38 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Itarana</t>
+          <t>Itapemirim</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3202900</v>
+        <v>3202801</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>229.69</v>
       </c>
       <c r="F104" t="n">
-        <v>289.81</v>
-      </c>
-      <c r="G104" t="n">
-        <v>306.44</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>274.35</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>219.98</v>
       </c>
       <c r="I104" t="n">
-        <v>278.91</v>
-      </c>
-      <c r="J104" t="n">
-        <v>288.65</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>272.88</v>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>6.1</v>
       </c>
       <c r="L104" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M104" t="n">
-        <v>5.3</v>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5100,44 +4664,44 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Itarana</t>
+          <t>Itapemirim</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3202900</v>
+        <v>3202801</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>257.58</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
+        <v>229.69</v>
+      </c>
+      <c r="F105" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="G105" t="n">
+        <v>290.06</v>
+      </c>
       <c r="H105" t="n">
-        <v>234.64</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+        <v>219.98</v>
+      </c>
+      <c r="I105" t="n">
+        <v>271.61</v>
+      </c>
+      <c r="J105" t="n">
+        <v>286.01</v>
+      </c>
       <c r="K105" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M105" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5190,44 +4754,38 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Iúna</t>
+          <t>Itarana</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3203007</v>
+        <v>3202900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>236.9</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
-        <v>220.78</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>289.81</v>
+      </c>
+      <c r="G107" t="n">
+        <v>306.44</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>278.91</v>
+      </c>
+      <c r="J107" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5235,44 +4793,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Iúna</t>
+          <t>Itarana</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3203007</v>
+        <v>3202900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>239.47</v>
-      </c>
-      <c r="F108" t="n">
-        <v>263.54</v>
-      </c>
-      <c r="G108" t="n">
-        <v>291.47</v>
-      </c>
+        <v>257.58</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>222.01</v>
-      </c>
-      <c r="I108" t="n">
-        <v>257.19</v>
-      </c>
-      <c r="J108" t="n">
-        <v>289.22</v>
-      </c>
+        <v>234.64</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L108" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M108" t="n">
-        <v>5</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5325,44 +4871,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jaguaré</t>
+          <t>Iúna</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3203056</v>
+        <v>3203007</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>238.89</v>
-      </c>
-      <c r="F110" t="n">
-        <v>278.17</v>
-      </c>
-      <c r="G110" t="n">
-        <v>289.28</v>
-      </c>
+        <v>236.9</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>225.44</v>
-      </c>
-      <c r="I110" t="n">
-        <v>268.07</v>
-      </c>
-      <c r="J110" t="n">
-        <v>291.15</v>
-      </c>
+        <v>220.78</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L110" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M110" t="n">
-        <v>5.1</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5370,37 +4904,43 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jaguaré</t>
+          <t>Iúna</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3203056</v>
+        <v>3203007</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>239.47</v>
+      </c>
       <c r="F111" t="n">
-        <v>285.54</v>
+        <v>263.54</v>
       </c>
       <c r="G111" t="n">
-        <v>289.28</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
+        <v>291.47</v>
+      </c>
+      <c r="H111" t="n">
+        <v>222.01</v>
+      </c>
       <c r="I111" t="n">
-        <v>273.18</v>
+        <v>257.19</v>
       </c>
       <c r="J111" t="n">
-        <v>291.15</v>
-      </c>
-      <c r="K111" t="inlineStr"/>
+        <v>289.22</v>
+      </c>
+      <c r="K111" t="n">
+        <v>6.3</v>
+      </c>
       <c r="L111" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="M111" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -5448,49 +4988,43 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jerônimo Monteiro</t>
+          <t>Jaguaré</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3203106</v>
+        <v>3203056</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>238.89</v>
       </c>
       <c r="F113" t="n">
-        <v>276.98</v>
+        <v>278.17</v>
       </c>
       <c r="G113" t="n">
-        <v>286.48</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>289.28</v>
+      </c>
+      <c r="H113" t="n">
+        <v>225.44</v>
       </c>
       <c r="I113" t="n">
-        <v>270.09</v>
+        <v>268.07</v>
       </c>
       <c r="J113" t="n">
-        <v>276.99</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>291.15</v>
+      </c>
+      <c r="K113" t="n">
+        <v>6.5</v>
       </c>
       <c r="L113" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M113" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="114">
@@ -5499,44 +5033,38 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jerônimo Monteiro</t>
+          <t>Jaguaré</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3203106</v>
+        <v>3203056</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>236.18</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="n">
-        <v>219.11</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>285.54</v>
+      </c>
+      <c r="G114" t="n">
+        <v>289.28</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>273.18</v>
+      </c>
+      <c r="J114" t="n">
+        <v>291.15</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>6</v>
+      </c>
+      <c r="M114" t="n">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5552,30 +5080,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>236.18</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
         <v>276.98</v>
       </c>
       <c r="G115" t="n">
         <v>286.48</v>
       </c>
-      <c r="H115" t="n">
-        <v>219.11</v>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
         <v>270.09</v>
       </c>
       <c r="J115" t="n">
         <v>276.99</v>
       </c>
-      <c r="K115" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>5.8</v>
       </c>
@@ -5589,11 +5111,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>João Neiva</t>
+          <t>Jerônimo Monteiro</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3203130</v>
+        <v>3203106</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -5601,31 +5123,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>233.31</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
+        <v>236.18</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>228.46</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
+        <v>219.11</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5634,11 +5144,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>João Neiva</t>
+          <t>Jerônimo Monteiro</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3203130</v>
+        <v>3203106</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -5646,37 +5156,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>233.31</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
+        <v>236.18</v>
+      </c>
+      <c r="F117" t="n">
+        <v>276.98</v>
       </c>
       <c r="G117" t="n">
-        <v>297.06</v>
+        <v>286.48</v>
       </c>
       <c r="H117" t="n">
-        <v>228.46</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
+        <v>219.11</v>
+      </c>
+      <c r="I117" t="n">
+        <v>270.09</v>
       </c>
       <c r="J117" t="n">
-        <v>297.99</v>
+        <v>276.99</v>
       </c>
       <c r="K117" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.4</v>
+      </c>
+      <c r="L117" t="n">
+        <v>5.8</v>
       </c>
       <c r="M117" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="118">
@@ -5693,24 +5197,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>233.31</v>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="n">
-        <v>297.06</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>228.46</v>
+      </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
-        <v>297.99</v>
-      </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>6.6</v>
+      </c>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5718,38 +5222,38 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Laranja da Terra</t>
+          <t>João Neiva</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3203163</v>
+        <v>3203130</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>250.75</v>
-      </c>
-      <c r="F119" t="n">
-        <v>314.47</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
+        <v>233.31</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
+        <v>297.06</v>
+      </c>
       <c r="H119" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="I119" t="n">
-        <v>304.63</v>
-      </c>
-      <c r="J119" t="inlineStr"/>
+        <v>228.46</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>297.99</v>
+      </c>
       <c r="K119" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L119" t="n">
-        <v>6</v>
-      </c>
-      <c r="M119" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5757,43 +5261,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Laranja da Terra</t>
+          <t>João Neiva</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3203163</v>
+        <v>3203130</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>286.33</v>
-      </c>
-      <c r="F120" t="n">
-        <v>293.64</v>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>316.49</v>
-      </c>
-      <c r="H120" t="n">
-        <v>260.07</v>
-      </c>
-      <c r="I120" t="n">
-        <v>283.92</v>
-      </c>
+        <v>297.06</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>308.6</v>
-      </c>
-      <c r="K120" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L120" t="n">
-        <v>6.2</v>
-      </c>
+        <v>297.99</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="121">
@@ -5847,11 +5339,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Linhares</t>
+          <t>Laranja da Terra</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3203205</v>
+        <v>3203163</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -5859,31 +5351,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229.19</v>
+        <v>286.33</v>
       </c>
       <c r="F122" t="n">
-        <v>255.72</v>
+        <v>293.64</v>
       </c>
       <c r="G122" t="n">
-        <v>281.47</v>
+        <v>316.49</v>
       </c>
       <c r="H122" t="n">
-        <v>204.02</v>
+        <v>260.07</v>
       </c>
       <c r="I122" t="n">
-        <v>256.78</v>
+        <v>283.92</v>
       </c>
       <c r="J122" t="n">
-        <v>283.42</v>
+        <v>308.6</v>
       </c>
       <c r="K122" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L122" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="M122" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="123">
@@ -5892,11 +5384,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Linhares</t>
+          <t>Laranja da Terra</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3203205</v>
+        <v>3203163</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -5904,24 +5396,24 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>231.83</v>
+        <v>250.75</v>
       </c>
       <c r="F123" t="n">
-        <v>269.07</v>
+        <v>314.47</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>220.59</v>
+        <v>229.1</v>
       </c>
       <c r="I123" t="n">
-        <v>268.25</v>
+        <v>304.63</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="L123" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="M123" t="inlineStr"/>
     </row>
@@ -5976,50 +5468,38 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mantenópolis</t>
+          <t>Linhares</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3203304</v>
+        <v>3203205</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>231.83</v>
       </c>
       <c r="F125" t="n">
-        <v>268.97</v>
-      </c>
-      <c r="G125" t="n">
-        <v>295.56</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>269.07</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>220.59</v>
       </c>
       <c r="I125" t="n">
-        <v>262.27</v>
-      </c>
-      <c r="J125" t="n">
-        <v>288.87</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>268.25</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>6.2</v>
       </c>
       <c r="L125" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M125" t="n">
-        <v>5.1</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6027,38 +5507,44 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mantenópolis</t>
+          <t>Linhares</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3203304</v>
+        <v>3203205</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>261.72</v>
+        <v>229.19</v>
       </c>
       <c r="F126" t="n">
-        <v>257.53</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
+        <v>255.72</v>
+      </c>
+      <c r="G126" t="n">
+        <v>281.47</v>
+      </c>
       <c r="H126" t="n">
-        <v>242.02</v>
+        <v>204.02</v>
       </c>
       <c r="I126" t="n">
-        <v>250.1</v>
-      </c>
-      <c r="J126" t="inlineStr"/>
+        <v>256.78</v>
+      </c>
+      <c r="J126" t="n">
+        <v>283.42</v>
+      </c>
       <c r="K126" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="L126" t="n">
         <v>5.1</v>
       </c>
-      <c r="M126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6074,36 +5560,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>261.72</v>
       </c>
       <c r="F127" t="n">
-        <v>266.92</v>
-      </c>
-      <c r="G127" t="n">
-        <v>295.56</v>
-      </c>
+        <v>257.53</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>242.02</v>
       </c>
       <c r="I127" t="n">
-        <v>260.1</v>
-      </c>
-      <c r="J127" t="n">
-        <v>288.87</v>
-      </c>
+        <v>250.1</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
         <v>7.3</v>
       </c>
       <c r="L127" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M127" t="n">
         <v>5.1</v>
       </c>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6111,49 +5591,43 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Marataízes</t>
+          <t>Mantenópolis</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3203320</v>
+        <v>3203304</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>261.72</v>
       </c>
       <c r="F128" t="n">
-        <v>268.1</v>
+        <v>266.92</v>
       </c>
       <c r="G128" t="n">
-        <v>309.86</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>295.56</v>
+      </c>
+      <c r="H128" t="n">
+        <v>242.02</v>
       </c>
       <c r="I128" t="n">
-        <v>259.76</v>
+        <v>260.1</v>
       </c>
       <c r="J128" t="n">
-        <v>304.99</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>288.87</v>
+      </c>
+      <c r="K128" t="n">
+        <v>7.3</v>
       </c>
       <c r="L128" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M128" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="129">
@@ -6162,38 +5636,38 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Marataízes</t>
+          <t>Mantenópolis</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3203320</v>
+        <v>3203304</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>236.32</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="n">
-        <v>280.9</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="n">
-        <v>224.01</v>
-      </c>
+        <v>268.97</v>
+      </c>
+      <c r="G129" t="n">
+        <v>295.56</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>278.44</v>
-      </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="n">
-        <v>6.5</v>
-      </c>
+        <v>262.27</v>
+      </c>
+      <c r="J129" t="n">
+        <v>288.87</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M129" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="M129" t="n">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6209,32 +5683,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>236.32</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="n">
-        <v>276.38</v>
+        <v>268.1</v>
       </c>
       <c r="G130" t="n">
         <v>309.86</v>
       </c>
-      <c r="H130" t="n">
-        <v>224.01</v>
-      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>271.84</v>
+        <v>259.76</v>
       </c>
       <c r="J130" t="n">
         <v>304.99</v>
       </c>
-      <c r="K130" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M130" t="n">
         <v>5.5</v>
@@ -6246,11 +5714,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Marechal Floriano</t>
+          <t>Marataízes</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3203346</v>
+        <v>3203320</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6258,24 +5726,24 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>245.23</v>
+        <v>236.32</v>
       </c>
       <c r="F131" t="n">
-        <v>269.45</v>
+        <v>280.9</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>229.36</v>
+        <v>224.01</v>
       </c>
       <c r="I131" t="n">
-        <v>265.82</v>
+        <v>278.44</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="L131" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="M131" t="inlineStr"/>
     </row>
@@ -6285,11 +5753,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Marechal Floriano</t>
+          <t>Marataízes</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3203346</v>
+        <v>3203320</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6297,31 +5765,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>245.23</v>
+        <v>236.32</v>
       </c>
       <c r="F132" t="n">
-        <v>276.04</v>
+        <v>276.38</v>
       </c>
       <c r="G132" t="n">
-        <v>323.38</v>
+        <v>309.86</v>
       </c>
       <c r="H132" t="n">
-        <v>229.36</v>
+        <v>224.01</v>
       </c>
       <c r="I132" t="n">
-        <v>272.16</v>
+        <v>271.84</v>
       </c>
       <c r="J132" t="n">
-        <v>309.83</v>
+        <v>304.99</v>
       </c>
       <c r="K132" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="L132" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M132" t="n">
         <v>5.5</v>
-      </c>
-      <c r="M132" t="n">
-        <v>5.8</v>
       </c>
     </row>
     <row r="133">
@@ -6369,11 +5837,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Marilândia</t>
+          <t>Marechal Floriano</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3203353</v>
+        <v>3203346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6381,30 +5849,24 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>281.08</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>245.23</v>
+      </c>
+      <c r="F134" t="n">
+        <v>269.45</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>263.29</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>229.36</v>
+      </c>
+      <c r="I134" t="n">
+        <v>265.82</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.8</v>
+      </c>
+      <c r="L134" t="n">
+        <v>5.3</v>
       </c>
       <c r="M134" t="inlineStr"/>
     </row>
@@ -6414,11 +5876,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Marilândia</t>
+          <t>Marechal Floriano</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3203353</v>
+        <v>3203346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6426,31 +5888,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>281.08</v>
+        <v>245.23</v>
       </c>
       <c r="F135" t="n">
-        <v>290.58</v>
+        <v>276.04</v>
       </c>
       <c r="G135" t="n">
-        <v>322.89</v>
+        <v>323.38</v>
       </c>
       <c r="H135" t="n">
-        <v>263.29</v>
+        <v>229.36</v>
       </c>
       <c r="I135" t="n">
-        <v>277.61</v>
+        <v>272.16</v>
       </c>
       <c r="J135" t="n">
-        <v>303.43</v>
+        <v>309.83</v>
       </c>
       <c r="K135" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="L135" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M135" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="136">
@@ -6467,26 +5929,32 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>281.08</v>
+      </c>
       <c r="F136" t="n">
         <v>290.58</v>
       </c>
       <c r="G136" t="n">
         <v>322.89</v>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>263.29</v>
+      </c>
       <c r="I136" t="n">
         <v>277.61</v>
       </c>
       <c r="J136" t="n">
         <v>303.43</v>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>8.1</v>
+      </c>
       <c r="L136" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M136" t="n">
         <v>5.7</v>
@@ -6498,49 +5966,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mimoso do Sul</t>
+          <t>Marilândia</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3203403</v>
+        <v>3203353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
-        <v>257.97</v>
+        <v>290.58</v>
       </c>
       <c r="G137" t="n">
-        <v>282.09</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>322.89</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
-        <v>256.05</v>
+        <v>277.61</v>
       </c>
       <c r="J137" t="n">
-        <v>280.22</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>303.43</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="M137" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="138">
@@ -6549,11 +6005,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mimoso do Sul</t>
+          <t>Marilândia</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3203403</v>
+        <v>3203353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -6561,31 +6017,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>242</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>281.08</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>227.56</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>263.29</v>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
@@ -6602,30 +6046,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>242</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>257.97</v>
       </c>
       <c r="G139" t="n">
         <v>282.09</v>
       </c>
-      <c r="H139" t="n">
-        <v>227.56</v>
-      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
         <v>256.05</v>
       </c>
       <c r="J139" t="n">
         <v>280.22</v>
       </c>
-      <c r="K139" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
         <v>5.2</v>
       </c>
@@ -6639,50 +6077,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Montanha</t>
+          <t>Mimoso do Sul</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3203502</v>
+        <v>3203403</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>232.51</v>
-      </c>
-      <c r="F140" t="n">
-        <v>267.96</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>218.77</v>
-      </c>
-      <c r="I140" t="n">
-        <v>265.91</v>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
+        <v>227.56</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L140" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>6.7</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6690,38 +6110,44 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Montanha</t>
+          <t>Mimoso do Sul</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3203502</v>
+        <v>3203403</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>232.51</v>
+        <v>242</v>
       </c>
       <c r="F141" t="n">
-        <v>287.01</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
+        <v>257.97</v>
+      </c>
+      <c r="G141" t="n">
+        <v>282.09</v>
+      </c>
       <c r="H141" t="n">
-        <v>218.77</v>
+        <v>227.56</v>
       </c>
       <c r="I141" t="n">
-        <v>289.74</v>
-      </c>
-      <c r="J141" t="inlineStr"/>
+        <v>256.05</v>
+      </c>
+      <c r="J141" t="n">
+        <v>280.22</v>
+      </c>
       <c r="K141" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="L141" t="n">
-        <v>6</v>
-      </c>
-      <c r="M141" t="inlineStr"/>
+        <v>5.2</v>
+      </c>
+      <c r="M141" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6740,33 +6166,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
         <v>258.65</v>
       </c>
       <c r="G142" t="n">
         <v>261.78</v>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
         <v>254.26</v>
       </c>
       <c r="J142" t="n">
         <v>281.78</v>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
         <v>5</v>
       </c>
@@ -6780,38 +6194,38 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mucurici</t>
+          <t>Montanha</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3203601</v>
+        <v>3203502</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>232.51</v>
+      </c>
       <c r="F143" t="n">
-        <v>250.43</v>
-      </c>
-      <c r="G143" t="n">
-        <v>264.99</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
+        <v>287.01</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>218.77</v>
+      </c>
       <c r="I143" t="n">
-        <v>247.25</v>
-      </c>
-      <c r="J143" t="n">
-        <v>266.71</v>
-      </c>
-      <c r="K143" t="inlineStr"/>
+        <v>289.74</v>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>6.3</v>
+      </c>
       <c r="L143" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M143" t="n">
-        <v>4.2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6819,36 +6233,36 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mucurici</t>
+          <t>Montanha</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3203601</v>
+        <v>3203502</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>240.11</v>
+        <v>232.51</v>
       </c>
       <c r="F144" t="n">
-        <v>250</v>
+        <v>267.96</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
-        <v>232.35</v>
+        <v>218.77</v>
       </c>
       <c r="I144" t="n">
-        <v>263.47</v>
+        <v>265.91</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="L144" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="M144" t="inlineStr"/>
     </row>
@@ -6866,36 +6280,30 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E145" t="n">
         <v>240.11</v>
       </c>
       <c r="F145" t="n">
-        <v>250.33</v>
-      </c>
-      <c r="G145" t="n">
-        <v>264.99</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>232.35</v>
       </c>
       <c r="I145" t="n">
-        <v>251.3</v>
-      </c>
-      <c r="J145" t="n">
-        <v>266.71</v>
-      </c>
+        <v>263.47</v>
+      </c>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="n">
         <v>6.6</v>
       </c>
       <c r="L145" t="n">
         <v>4.8</v>
       </c>
-      <c r="M145" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6903,43 +6311,43 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Muniz Freire</t>
+          <t>Mucurici</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3203700</v>
+        <v>3203601</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>251.75</v>
+        <v>240.11</v>
       </c>
       <c r="F146" t="n">
-        <v>272.11</v>
+        <v>250.33</v>
       </c>
       <c r="G146" t="n">
-        <v>311.86</v>
+        <v>264.99</v>
       </c>
       <c r="H146" t="n">
-        <v>243.18</v>
+        <v>232.35</v>
       </c>
       <c r="I146" t="n">
-        <v>278.75</v>
+        <v>251.3</v>
       </c>
       <c r="J146" t="n">
-        <v>295.05</v>
+        <v>266.71</v>
       </c>
       <c r="K146" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L146" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="M146" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="147">
@@ -6948,38 +6356,38 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Muniz Freire</t>
+          <t>Mucurici</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3203700</v>
+        <v>3203601</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>249.48</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="n">
-        <v>234.65</v>
-      </c>
+        <v>250.43</v>
+      </c>
+      <c r="G147" t="n">
+        <v>264.99</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>275.88</v>
-      </c>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="n">
-        <v>7</v>
-      </c>
+        <v>247.25</v>
+      </c>
+      <c r="J147" t="n">
+        <v>266.71</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M147" t="inlineStr"/>
+        <v>4.9</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7032,50 +6440,38 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Muqui</t>
+          <t>Muniz Freire</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3203809</v>
+        <v>3203700</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>249.48</v>
       </c>
       <c r="F149" t="n">
-        <v>270</v>
-      </c>
-      <c r="G149" t="n">
-        <v>298.16</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>276.7</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>234.65</v>
       </c>
       <c r="I149" t="n">
-        <v>268.03</v>
-      </c>
-      <c r="J149" t="n">
-        <v>297.68</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>275.88</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="n">
+        <v>7</v>
       </c>
       <c r="L149" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M149" t="n">
-        <v>5.3</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7083,38 +6479,44 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Muqui</t>
+          <t>Muniz Freire</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3203809</v>
+        <v>3203700</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>246.34</v>
+        <v>251.75</v>
       </c>
       <c r="F150" t="n">
-        <v>297.3</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
+        <v>272.11</v>
+      </c>
+      <c r="G150" t="n">
+        <v>311.86</v>
+      </c>
       <c r="H150" t="n">
-        <v>232.24</v>
+        <v>243.18</v>
       </c>
       <c r="I150" t="n">
-        <v>270.76</v>
-      </c>
-      <c r="J150" t="inlineStr"/>
+        <v>278.75</v>
+      </c>
+      <c r="J150" t="n">
+        <v>295.05</v>
+      </c>
       <c r="K150" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L150" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M150" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="M150" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7167,43 +6569,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nova Venécia</t>
+          <t>Muqui</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3203908</v>
+        <v>3203809</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E152" t="n">
-        <v>255.32</v>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="n">
-        <v>285.94</v>
+        <v>270</v>
       </c>
       <c r="G152" t="n">
-        <v>311.21</v>
-      </c>
-      <c r="H152" t="n">
-        <v>233.12</v>
-      </c>
+        <v>298.16</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>267.73</v>
+        <v>268.03</v>
       </c>
       <c r="J152" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="K152" t="n">
-        <v>7</v>
-      </c>
+        <v>297.68</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M152" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="153">
@@ -7212,11 +6608,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nova Venécia</t>
+          <t>Muqui</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3203908</v>
+        <v>3203809</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -7224,24 +6620,24 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>251.55</v>
+        <v>246.34</v>
       </c>
       <c r="F153" t="n">
-        <v>283.66</v>
+        <v>297.3</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="n">
-        <v>239.28</v>
+        <v>232.24</v>
       </c>
       <c r="I153" t="n">
-        <v>274.11</v>
+        <v>270.76</v>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="L153" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="M153" t="inlineStr"/>
     </row>
@@ -7296,43 +6692,43 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Pancas</t>
+          <t>Nova Venécia</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3204005</v>
+        <v>3203908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221.2</v>
+        <v>255.32</v>
       </c>
       <c r="F155" t="n">
-        <v>250.56</v>
+        <v>285.94</v>
       </c>
       <c r="G155" t="n">
-        <v>272.84</v>
+        <v>311.21</v>
       </c>
       <c r="H155" t="n">
-        <v>214.49</v>
+        <v>233.12</v>
       </c>
       <c r="I155" t="n">
-        <v>252.08</v>
+        <v>267.73</v>
       </c>
       <c r="J155" t="n">
-        <v>276.95</v>
+        <v>295.52</v>
       </c>
       <c r="K155" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="L155" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="M155" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="156">
@@ -7341,44 +6737,38 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Pancas</t>
+          <t>Nova Venécia</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3204005</v>
+        <v>3203908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219.49</v>
+        <v>251.55</v>
       </c>
       <c r="F156" t="n">
-        <v>242.62</v>
-      </c>
-      <c r="G156" t="n">
-        <v>272.84</v>
-      </c>
+        <v>283.66</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="n">
-        <v>229.68</v>
+        <v>239.28</v>
       </c>
       <c r="I156" t="n">
-        <v>248.88</v>
-      </c>
-      <c r="J156" t="n">
-        <v>276.95</v>
-      </c>
+        <v>274.11</v>
+      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="n">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="L156" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M156" t="n">
-        <v>4.7</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7394,30 +6784,36 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221.46</v>
+        <v>219.49</v>
       </c>
       <c r="F157" t="n">
-        <v>252.48</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
+        <v>242.62</v>
+      </c>
+      <c r="G157" t="n">
+        <v>272.84</v>
+      </c>
       <c r="H157" t="n">
-        <v>212.14</v>
+        <v>229.68</v>
       </c>
       <c r="I157" t="n">
-        <v>252.85</v>
-      </c>
-      <c r="J157" t="inlineStr"/>
+        <v>248.88</v>
+      </c>
+      <c r="J157" t="n">
+        <v>276.95</v>
+      </c>
       <c r="K157" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="L157" t="n">
-        <v>5</v>
-      </c>
-      <c r="M157" t="inlineStr"/>
+        <v>4.9</v>
+      </c>
+      <c r="M157" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7425,50 +6821,38 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Pedro Canário</t>
+          <t>Pancas</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3204054</v>
+        <v>3204005</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>221.46</v>
       </c>
       <c r="F158" t="n">
-        <v>262.71</v>
-      </c>
-      <c r="G158" t="n">
-        <v>297.65</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>252.48</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>212.14</v>
       </c>
       <c r="I158" t="n">
-        <v>261.2</v>
-      </c>
-      <c r="J158" t="n">
-        <v>288.85</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>252.85</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>6</v>
       </c>
       <c r="L158" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M158" t="n">
-        <v>5.2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7476,44 +6860,44 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Pedro Canário</t>
+          <t>Pancas</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3204054</v>
+        <v>3204005</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229.56</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
+        <v>221.2</v>
+      </c>
+      <c r="F159" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="G159" t="n">
+        <v>272.84</v>
+      </c>
       <c r="H159" t="n">
-        <v>214.16</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
+        <v>214.49</v>
+      </c>
+      <c r="I159" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="J159" t="n">
+        <v>276.95</v>
+      </c>
       <c r="K159" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="L159" t="n">
+        <v>5</v>
+      </c>
+      <c r="M159" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7529,36 +6913,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E160" t="n">
         <v>229.56</v>
       </c>
-      <c r="F160" t="n">
-        <v>262.71</v>
-      </c>
-      <c r="G160" t="n">
-        <v>297.65</v>
-      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="n">
         <v>214.16</v>
       </c>
-      <c r="I160" t="n">
-        <v>261.2</v>
-      </c>
-      <c r="J160" t="n">
-        <v>288.85</v>
-      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="n">
         <v>6.2</v>
       </c>
-      <c r="L160" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M160" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7566,40 +6938,34 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pinheiros</t>
+          <t>Pedro Canário</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3204104</v>
+        <v>3204054</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E161" t="n">
-        <v>268.49</v>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>300.08</v>
+        <v>262.71</v>
       </c>
       <c r="G161" t="n">
-        <v>295.56</v>
-      </c>
-      <c r="H161" t="n">
-        <v>251.13</v>
-      </c>
+        <v>297.65</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>298.43</v>
+        <v>261.2</v>
       </c>
       <c r="J161" t="n">
-        <v>293.44</v>
-      </c>
-      <c r="K161" t="n">
-        <v>7.7</v>
-      </c>
+        <v>288.85</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="M161" t="n">
         <v>5.2</v>
@@ -7611,38 +6977,44 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Pinheiros</t>
+          <t>Pedro Canário</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3204104</v>
+        <v>3204054</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>235.39</v>
+        <v>229.56</v>
       </c>
       <c r="F162" t="n">
-        <v>267.32</v>
-      </c>
-      <c r="G162" t="inlineStr"/>
+        <v>262.71</v>
+      </c>
+      <c r="G162" t="n">
+        <v>297.65</v>
+      </c>
       <c r="H162" t="n">
-        <v>227.93</v>
+        <v>214.16</v>
       </c>
       <c r="I162" t="n">
-        <v>262.36</v>
-      </c>
-      <c r="J162" t="inlineStr"/>
+        <v>261.2</v>
+      </c>
+      <c r="J162" t="n">
+        <v>288.85</v>
+      </c>
       <c r="K162" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L162" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M162" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="M162" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7658,32 +7030,32 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>238.54</v>
+        <v>268.49</v>
       </c>
       <c r="F163" t="n">
-        <v>272.67</v>
+        <v>300.08</v>
       </c>
       <c r="G163" t="n">
         <v>295.56</v>
       </c>
       <c r="H163" t="n">
-        <v>230.13</v>
+        <v>251.13</v>
       </c>
       <c r="I163" t="n">
-        <v>268.25</v>
+        <v>298.43</v>
       </c>
       <c r="J163" t="n">
         <v>293.44</v>
       </c>
       <c r="K163" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="L163" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="M163" t="n">
         <v>5.2</v>
@@ -7695,50 +7067,38 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Piúma</t>
+          <t>Pinheiros</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3204203</v>
+        <v>3204104</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>241.01</v>
+        <v>235.39</v>
       </c>
       <c r="F164" t="n">
-        <v>279.32</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
+        <v>267.32</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="n">
-        <v>229.51</v>
+        <v>227.93</v>
       </c>
       <c r="I164" t="n">
-        <v>277.09</v>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
+        <v>262.36</v>
+      </c>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="n">
         <v>6.6</v>
       </c>
       <c r="L164" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7746,37 +7106,43 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Piúma</t>
+          <t>Pinheiros</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3204203</v>
+        <v>3204104</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>238.54</v>
+      </c>
       <c r="F165" t="n">
-        <v>282.43</v>
+        <v>272.67</v>
       </c>
       <c r="G165" t="n">
-        <v>280.71</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
+        <v>295.56</v>
+      </c>
+      <c r="H165" t="n">
+        <v>230.13</v>
+      </c>
       <c r="I165" t="n">
-        <v>279.32</v>
+        <v>268.25</v>
       </c>
       <c r="J165" t="n">
-        <v>281.12</v>
-      </c>
-      <c r="K165" t="inlineStr"/>
+        <v>293.44</v>
+      </c>
+      <c r="K165" t="n">
+        <v>6.7</v>
+      </c>
       <c r="L165" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M165" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="166">
@@ -7793,30 +7159,30 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>241.01</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="n">
-        <v>278.4</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="n">
-        <v>229.51</v>
-      </c>
+        <v>282.43</v>
+      </c>
+      <c r="G166" t="n">
+        <v>280.71</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>276.43</v>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="n">
-        <v>6.6</v>
-      </c>
+        <v>279.32</v>
+      </c>
+      <c r="J166" t="n">
+        <v>281.12</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M166" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M166" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7824,11 +7190,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ponto Belo</t>
+          <t>Piúma</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3204252</v>
+        <v>3204203</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -7836,24 +7202,24 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>225.85</v>
+        <v>241.01</v>
       </c>
       <c r="F167" t="n">
-        <v>264.5</v>
+        <v>278.4</v>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>223.37</v>
+        <v>229.51</v>
       </c>
       <c r="I167" t="n">
-        <v>262.81</v>
+        <v>276.43</v>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="L167" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="M167" t="inlineStr"/>
     </row>
@@ -7863,11 +7229,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ponto Belo</t>
+          <t>Piúma</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3204252</v>
+        <v>3204203</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -7875,32 +7241,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>225.85</v>
+        <v>241.01</v>
       </c>
       <c r="F168" t="n">
-        <v>265.41</v>
-      </c>
-      <c r="G168" t="n">
-        <v>272.1</v>
-      </c>
+        <v>279.32</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="n">
-        <v>223.37</v>
+        <v>229.51</v>
       </c>
       <c r="I168" t="n">
-        <v>263.43</v>
-      </c>
-      <c r="J168" t="n">
-        <v>278.24</v>
-      </c>
+        <v>277.09</v>
+      </c>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="L168" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M168" t="n">
-        <v>4.7</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7919,33 +7279,21 @@
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
         <v>265.58</v>
       </c>
       <c r="G169" t="n">
         <v>272.1</v>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>263.54</v>
       </c>
       <c r="J169" t="n">
         <v>278.24</v>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
         <v>5.4</v>
       </c>
@@ -7959,56 +7307,38 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Presidente Kennedy</t>
+          <t>Ponto Belo</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3204302</v>
+        <v>3204252</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G170" t="n">
-        <v>317.26</v>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J170" t="n">
-        <v>293.13</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M170" t="n">
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>225.85</v>
+      </c>
+      <c r="F170" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="n">
+        <v>223.37</v>
+      </c>
+      <c r="I170" t="n">
+        <v>262.81</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L170" t="n">
         <v>5.5</v>
       </c>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8016,38 +7346,44 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Presidente Kennedy</t>
+          <t>Ponto Belo</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3204302</v>
+        <v>3204252</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>247.08</v>
+        <v>225.85</v>
       </c>
       <c r="F171" t="n">
-        <v>269.82</v>
-      </c>
-      <c r="G171" t="inlineStr"/>
+        <v>265.41</v>
+      </c>
+      <c r="G171" t="n">
+        <v>272.1</v>
+      </c>
       <c r="H171" t="n">
-        <v>231.35</v>
+        <v>223.37</v>
       </c>
       <c r="I171" t="n">
-        <v>262.61</v>
-      </c>
-      <c r="J171" t="inlineStr"/>
+        <v>263.43</v>
+      </c>
+      <c r="J171" t="n">
+        <v>278.24</v>
+      </c>
       <c r="K171" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="L171" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M171" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="M171" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8063,33 +7399,21 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>247.08</v>
-      </c>
-      <c r="F172" t="n">
-        <v>269.82</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
         <v>317.26</v>
       </c>
-      <c r="H172" t="n">
-        <v>231.35</v>
-      </c>
-      <c r="I172" t="n">
-        <v>262.61</v>
-      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
         <v>293.13</v>
       </c>
-      <c r="K172" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L172" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
       <c r="M172" t="n">
         <v>5.5</v>
       </c>
@@ -8100,11 +7424,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Rio Bananal</t>
+          <t>Presidente Kennedy</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3204351</v>
+        <v>3204302</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -8112,24 +7436,24 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>239.21</v>
+        <v>247.08</v>
       </c>
       <c r="F173" t="n">
-        <v>258.99</v>
+        <v>269.82</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>224.68</v>
+        <v>231.35</v>
       </c>
       <c r="I173" t="n">
-        <v>261.18</v>
+        <v>262.61</v>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L173" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="M173" t="inlineStr"/>
     </row>
@@ -8139,11 +7463,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Rio Bananal</t>
+          <t>Presidente Kennedy</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3204351</v>
+        <v>3204302</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -8151,31 +7475,31 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>239.21</v>
+        <v>247.08</v>
       </c>
       <c r="F174" t="n">
-        <v>258.99</v>
+        <v>269.82</v>
       </c>
       <c r="G174" t="n">
-        <v>284.33</v>
+        <v>317.26</v>
       </c>
       <c r="H174" t="n">
-        <v>224.68</v>
+        <v>231.35</v>
       </c>
       <c r="I174" t="n">
-        <v>261.18</v>
+        <v>262.61</v>
       </c>
       <c r="J174" t="n">
-        <v>278.94</v>
+        <v>293.13</v>
       </c>
       <c r="K174" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L174" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="M174" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="175">
@@ -8196,29 +7520,17 @@
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
         <v>284.33</v>
       </c>
       <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
         <v>278.94</v>
       </c>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
       <c r="M175" t="n">
         <v>4.8</v>
       </c>
@@ -8229,37 +7541,43 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Rio Novo do Sul</t>
+          <t>Rio Bananal</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3204401</v>
+        <v>3204351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>239.21</v>
+      </c>
       <c r="F176" t="n">
-        <v>287.48</v>
+        <v>258.99</v>
       </c>
       <c r="G176" t="n">
-        <v>300.7</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
+        <v>284.33</v>
+      </c>
+      <c r="H176" t="n">
+        <v>224.68</v>
+      </c>
       <c r="I176" t="n">
-        <v>273.55</v>
+        <v>261.18</v>
       </c>
       <c r="J176" t="n">
-        <v>292.28</v>
-      </c>
-      <c r="K176" t="inlineStr"/>
+        <v>278.94</v>
+      </c>
+      <c r="K176" t="n">
+        <v>6.6</v>
+      </c>
       <c r="L176" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="M176" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="177">
@@ -8268,44 +7586,38 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Rio Novo do Sul</t>
+          <t>Rio Bananal</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3204401</v>
+        <v>3204351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>237.16</v>
+        <v>239.21</v>
       </c>
       <c r="F177" t="n">
-        <v>287.48</v>
-      </c>
-      <c r="G177" t="n">
-        <v>300.7</v>
-      </c>
+        <v>258.99</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
-        <v>229.28</v>
+        <v>224.68</v>
       </c>
       <c r="I177" t="n">
-        <v>273.55</v>
-      </c>
-      <c r="J177" t="n">
-        <v>292.28</v>
-      </c>
+        <v>261.18</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="n">
         <v>6.6</v>
       </c>
       <c r="L177" t="n">
-        <v>6</v>
-      </c>
-      <c r="M177" t="n">
-        <v>5.3</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8321,24 +7633,36 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E178" t="n">
         <v>237.16</v>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>287.48</v>
+      </c>
+      <c r="G178" t="n">
+        <v>300.7</v>
+      </c>
       <c r="H178" t="n">
         <v>229.28</v>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+      <c r="I178" t="n">
+        <v>273.55</v>
+      </c>
+      <c r="J178" t="n">
+        <v>292.28</v>
+      </c>
       <c r="K178" t="n">
         <v>6.6</v>
       </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
+      <c r="L178" t="n">
+        <v>6</v>
+      </c>
+      <c r="M178" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8346,32 +7670,38 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Santa Leopoldina</t>
+          <t>Rio Novo do Sul</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3204500</v>
+        <v>3204401</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>251.61</v>
-      </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="n">
-        <v>231.45</v>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>287.48</v>
+      </c>
+      <c r="G179" t="n">
+        <v>300.7</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>273.55</v>
+      </c>
+      <c r="J179" t="n">
+        <v>292.28</v>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="n">
+        <v>6</v>
+      </c>
+      <c r="M179" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8379,50 +7709,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Santa Leopoldina</t>
+          <t>Rio Novo do Sul</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>3204500</v>
+        <v>3204401</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F180" t="n">
-        <v>273.84</v>
-      </c>
-      <c r="G180" t="n">
-        <v>288.35</v>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
-        <v>276.03</v>
-      </c>
-      <c r="J180" t="n">
-        <v>279.59</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L180" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M180" t="n">
-        <v>4.9</v>
-      </c>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8438,36 +7750,24 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E181" t="n">
         <v>251.61</v>
       </c>
-      <c r="F181" t="n">
-        <v>273.84</v>
-      </c>
-      <c r="G181" t="n">
-        <v>288.35</v>
-      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="n">
         <v>231.45</v>
       </c>
-      <c r="I181" t="n">
-        <v>276.03</v>
-      </c>
-      <c r="J181" t="n">
-        <v>279.59</v>
-      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="n">
         <v>6.9</v>
       </c>
-      <c r="L181" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M181" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8475,38 +7775,38 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Santa Maria de Jetibá</t>
+          <t>Santa Leopoldina</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3204559</v>
+        <v>3204500</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
-        <v>252.67</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>311.33</v>
-      </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="n">
-        <v>236.57</v>
-      </c>
+        <v>273.84</v>
+      </c>
+      <c r="G182" t="n">
+        <v>288.35</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
-        <v>306.49</v>
-      </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="n">
-        <v>6.9</v>
-      </c>
+        <v>276.03</v>
+      </c>
+      <c r="J182" t="n">
+        <v>279.59</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M182" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="M182" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -8514,43 +7814,43 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Santa Maria de Jetibá</t>
+          <t>Santa Leopoldina</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>3204559</v>
+        <v>3204500</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>254.82</v>
+        <v>251.61</v>
       </c>
       <c r="F183" t="n">
-        <v>289.92</v>
+        <v>273.84</v>
       </c>
       <c r="G183" t="n">
-        <v>307.79</v>
+        <v>288.35</v>
       </c>
       <c r="H183" t="n">
-        <v>237.1</v>
+        <v>231.45</v>
       </c>
       <c r="I183" t="n">
-        <v>278.06</v>
+        <v>276.03</v>
       </c>
       <c r="J183" t="n">
-        <v>297.06</v>
+        <v>279.59</v>
       </c>
       <c r="K183" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="L183" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M183" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="184">
@@ -8604,44 +7904,38 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Santa Teresa</t>
+          <t>Santa Maria de Jetibá</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3204609</v>
+        <v>3204559</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>260.95</v>
+        <v>252.67</v>
       </c>
       <c r="F185" t="n">
-        <v>290.11</v>
-      </c>
-      <c r="G185" t="n">
-        <v>308.36</v>
-      </c>
+        <v>311.33</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="n">
-        <v>242.84</v>
+        <v>236.57</v>
       </c>
       <c r="I185" t="n">
-        <v>282.8</v>
-      </c>
-      <c r="J185" t="n">
-        <v>304.03</v>
-      </c>
+        <v>306.49</v>
+      </c>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="L185" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M185" t="n">
-        <v>5.5</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8649,43 +7943,43 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Santa Teresa</t>
+          <t>Santa Maria de Jetibá</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3204609</v>
+        <v>3204559</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Estadual</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>252.85</v>
+        <v>254.82</v>
       </c>
       <c r="F186" t="n">
-        <v>282.51</v>
+        <v>289.92</v>
       </c>
       <c r="G186" t="n">
-        <v>304.95</v>
+        <v>307.79</v>
       </c>
       <c r="H186" t="n">
-        <v>237.42</v>
+        <v>237.1</v>
       </c>
       <c r="I186" t="n">
-        <v>278.91</v>
+        <v>278.06</v>
       </c>
       <c r="J186" t="n">
-        <v>300.67</v>
+        <v>297.06</v>
       </c>
       <c r="K186" t="n">
         <v>7.1</v>
       </c>
       <c r="L186" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M186" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="187">
@@ -8702,30 +7996,36 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>251.82</v>
+        <v>252.85</v>
       </c>
       <c r="F187" t="n">
-        <v>278.83</v>
-      </c>
-      <c r="G187" t="inlineStr"/>
+        <v>282.51</v>
+      </c>
+      <c r="G187" t="n">
+        <v>304.95</v>
+      </c>
       <c r="H187" t="n">
-        <v>236.73</v>
+        <v>237.42</v>
       </c>
       <c r="I187" t="n">
-        <v>277.03</v>
-      </c>
-      <c r="J187" t="inlineStr"/>
+        <v>278.91</v>
+      </c>
+      <c r="J187" t="n">
+        <v>300.67</v>
+      </c>
       <c r="K187" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="L187" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M187" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="M187" t="n">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8733,11 +8033,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Serra</t>
+          <t>Santa Teresa</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3205002</v>
+        <v>3204609</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -8745,31 +8045,31 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>233.8</v>
+        <v>260.95</v>
       </c>
       <c r="F188" t="n">
-        <v>262.1</v>
+        <v>290.11</v>
       </c>
       <c r="G188" t="n">
-        <v>278.69</v>
+        <v>308.36</v>
       </c>
       <c r="H188" t="n">
-        <v>229.14</v>
+        <v>242.84</v>
       </c>
       <c r="I188" t="n">
-        <v>267.78</v>
+        <v>282.8</v>
       </c>
       <c r="J188" t="n">
-        <v>284.49</v>
+        <v>304.03</v>
       </c>
       <c r="K188" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="L188" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M188" t="n">
         <v>5.5</v>
-      </c>
-      <c r="M188" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="189">
@@ -8778,11 +8078,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Serra</t>
+          <t>Santa Teresa</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3205002</v>
+        <v>3204609</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -8790,24 +8090,24 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220.75</v>
+        <v>251.82</v>
       </c>
       <c r="F189" t="n">
-        <v>252.51</v>
+        <v>278.83</v>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>210.81</v>
+        <v>236.73</v>
       </c>
       <c r="I189" t="n">
-        <v>252.74</v>
+        <v>277.03</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="L189" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="M189" t="inlineStr"/>
     </row>
@@ -8862,55 +8162,43 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sooretama</t>
+          <t>Serra</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3205010</v>
+        <v>3205002</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E191" t="n">
+        <v>233.8</v>
+      </c>
+      <c r="F191" t="n">
+        <v>262.1</v>
       </c>
       <c r="G191" t="n">
-        <v>275.73</v>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>278.69</v>
+      </c>
+      <c r="H191" t="n">
+        <v>229.14</v>
+      </c>
+      <c r="I191" t="n">
+        <v>267.78</v>
       </c>
       <c r="J191" t="n">
-        <v>281.99</v>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>284.49</v>
+      </c>
+      <c r="K191" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L191" t="n">
+        <v>5.5</v>
       </c>
       <c r="M191" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="192">
@@ -8919,11 +8207,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Sooretama</t>
+          <t>Serra</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3205010</v>
+        <v>3205002</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -8931,24 +8219,24 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>217.8</v>
+        <v>220.75</v>
       </c>
       <c r="F192" t="n">
-        <v>250.85</v>
+        <v>252.51</v>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="n">
-        <v>208.24</v>
+        <v>210.81</v>
       </c>
       <c r="I192" t="n">
-        <v>256.29</v>
+        <v>252.74</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="n">
         <v>5.9</v>
       </c>
       <c r="L192" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M192" t="inlineStr"/>
     </row>
@@ -8966,33 +8254,21 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
-        <v>217.8</v>
-      </c>
-      <c r="F193" t="n">
-        <v>250.85</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
         <v>275.73</v>
       </c>
-      <c r="H193" t="n">
-        <v>208.24</v>
-      </c>
-      <c r="I193" t="n">
-        <v>256.29</v>
-      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
         <v>281.99</v>
       </c>
-      <c r="K193" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L193" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
       <c r="M193" t="n">
         <v>4.7</v>
       </c>
@@ -9003,44 +8279,38 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>São Domingos do Norte</t>
+          <t>Sooretama</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3204658</v>
+        <v>3205010</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>227.15</v>
+        <v>217.8</v>
       </c>
       <c r="F194" t="n">
-        <v>250.17</v>
-      </c>
-      <c r="G194" t="n">
-        <v>275.6</v>
-      </c>
+        <v>250.85</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
-        <v>228.04</v>
+        <v>208.24</v>
       </c>
       <c r="I194" t="n">
-        <v>252.49</v>
-      </c>
-      <c r="J194" t="n">
-        <v>287.8</v>
-      </c>
+        <v>256.29</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L194" t="n">
         <v>5</v>
       </c>
-      <c r="M194" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9048,44 +8318,44 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>São Domingos do Norte</t>
+          <t>Sooretama</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3204658</v>
+        <v>3205010</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>227.15</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+        <v>217.8</v>
+      </c>
+      <c r="F195" t="n">
+        <v>250.85</v>
+      </c>
+      <c r="G195" t="n">
+        <v>275.73</v>
+      </c>
       <c r="H195" t="n">
-        <v>228.04</v>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
+        <v>208.24</v>
+      </c>
+      <c r="I195" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="J195" t="n">
+        <v>281.99</v>
+      </c>
       <c r="K195" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="L195" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9101,35 +8371,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>227.15</v>
       </c>
       <c r="F196" t="n">
-        <v>248.15</v>
+        <v>250.17</v>
       </c>
       <c r="G196" t="n">
         <v>275.6</v>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H196" t="n">
+        <v>228.04</v>
       </c>
       <c r="I196" t="n">
-        <v>252.84</v>
+        <v>252.49</v>
       </c>
       <c r="J196" t="n">
         <v>287.8</v>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K196" t="n">
+        <v>6.4</v>
       </c>
       <c r="L196" t="n">
         <v>5</v>
@@ -9144,11 +8408,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>São Gabriel da Palha</t>
+          <t>São Domingos do Norte</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3204708</v>
+        <v>3204658</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -9156,25 +8420,19 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>250.24</v>
-      </c>
-      <c r="F197" t="n">
-        <v>265.16</v>
-      </c>
+        <v>227.15</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="n">
-        <v>236.34</v>
-      </c>
-      <c r="I197" t="n">
-        <v>265.07</v>
-      </c>
+        <v>228.04</v>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="n">
-        <v>7</v>
-      </c>
-      <c r="L197" t="n">
-        <v>5.1</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -9183,43 +8441,37 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>São Gabriel da Palha</t>
+          <t>São Domingos do Norte</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3204708</v>
+        <v>3204658</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
-        <v>250.24</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>282.12</v>
+        <v>248.15</v>
       </c>
       <c r="G198" t="n">
-        <v>305.39</v>
-      </c>
-      <c r="H198" t="n">
-        <v>236.34</v>
-      </c>
+        <v>275.6</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>274.68</v>
+        <v>252.84</v>
       </c>
       <c r="J198" t="n">
-        <v>298.75</v>
-      </c>
-      <c r="K198" t="n">
-        <v>7</v>
-      </c>
+        <v>287.8</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="M198" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="199">
@@ -9236,42 +8488,30 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>250.24</v>
       </c>
       <c r="F199" t="n">
-        <v>308.3</v>
-      </c>
-      <c r="G199" t="n">
-        <v>305.39</v>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>265.16</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="n">
+        <v>236.34</v>
       </c>
       <c r="I199" t="n">
-        <v>289.51</v>
-      </c>
-      <c r="J199" t="n">
-        <v>298.75</v>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>265.07</v>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="n">
+        <v>7</v>
       </c>
       <c r="L199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M199" t="n">
-        <v>5.4</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9279,11 +8519,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>São José do Calçado</t>
+          <t>São Gabriel da Palha</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3204807</v>
+        <v>3204708</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -9291,31 +8531,25 @@
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F200" t="n">
+        <v>308.3</v>
       </c>
       <c r="G200" t="n">
-        <v>274.6</v>
+        <v>305.39</v>
       </c>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I200" t="n">
+        <v>289.51</v>
       </c>
       <c r="J200" t="n">
-        <v>275.54</v>
+        <v>298.75</v>
       </c>
       <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L200" t="n">
+        <v>6.6</v>
       </c>
       <c r="M200" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="201">
@@ -9324,38 +8558,44 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>São José do Calçado</t>
+          <t>São Gabriel da Palha</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3204807</v>
+        <v>3204708</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220.95</v>
+        <v>250.24</v>
       </c>
       <c r="F201" t="n">
-        <v>246.98</v>
-      </c>
-      <c r="G201" t="inlineStr"/>
+        <v>282.12</v>
+      </c>
+      <c r="G201" t="n">
+        <v>305.39</v>
+      </c>
       <c r="H201" t="n">
-        <v>209.24</v>
+        <v>236.34</v>
       </c>
       <c r="I201" t="n">
-        <v>249.85</v>
-      </c>
-      <c r="J201" t="inlineStr"/>
+        <v>274.68</v>
+      </c>
+      <c r="J201" t="n">
+        <v>298.75</v>
+      </c>
       <c r="K201" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L201" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M201" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="M201" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9371,7 +8611,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -9380,27 +8620,21 @@
       <c r="F202" t="n">
         <v>246.98</v>
       </c>
-      <c r="G202" t="n">
-        <v>274.6</v>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="n">
         <v>209.24</v>
       </c>
       <c r="I202" t="n">
         <v>249.85</v>
       </c>
-      <c r="J202" t="n">
-        <v>275.54</v>
-      </c>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="n">
         <v>6</v>
       </c>
       <c r="L202" t="n">
         <v>4.9</v>
       </c>
-      <c r="M202" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9408,11 +8642,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>São Mateus</t>
+          <t>São José do Calçado</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3204906</v>
+        <v>3204807</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -9420,31 +8654,31 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>224.11</v>
+        <v>220.95</v>
       </c>
       <c r="F203" t="n">
-        <v>270.52</v>
+        <v>246.98</v>
       </c>
       <c r="G203" t="n">
-        <v>284.02</v>
+        <v>274.6</v>
       </c>
       <c r="H203" t="n">
-        <v>214.99</v>
+        <v>209.24</v>
       </c>
       <c r="I203" t="n">
-        <v>269.52</v>
+        <v>249.85</v>
       </c>
       <c r="J203" t="n">
-        <v>283.58</v>
+        <v>275.54</v>
       </c>
       <c r="K203" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="L203" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="M203" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="204">
@@ -9453,38 +8687,32 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>São Mateus</t>
+          <t>São José do Calçado</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3204906</v>
+        <v>3204807</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
-        <v>223.58</v>
-      </c>
-      <c r="F204" t="n">
-        <v>263.14</v>
-      </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="n">
-        <v>214.84</v>
-      </c>
-      <c r="I204" t="n">
-        <v>261.49</v>
-      </c>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="n">
-        <v>6</v>
-      </c>
-      <c r="L204" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M204" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="n">
+        <v>274.6</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="n">
+        <v>275.54</v>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9537,11 +8765,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>São Roque do Canaã</t>
+          <t>São Mateus</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3204955</v>
+        <v>3204906</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -9549,31 +8777,31 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>270.93</v>
+        <v>224.11</v>
       </c>
       <c r="F206" t="n">
-        <v>284.9</v>
+        <v>270.52</v>
       </c>
       <c r="G206" t="n">
-        <v>297.41</v>
+        <v>284.02</v>
       </c>
       <c r="H206" t="n">
-        <v>240.12</v>
+        <v>214.99</v>
       </c>
       <c r="I206" t="n">
-        <v>279.35</v>
+        <v>269.52</v>
       </c>
       <c r="J206" t="n">
-        <v>289.58</v>
+        <v>283.58</v>
       </c>
       <c r="K206" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="L206" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="M206" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="207">
@@ -9582,11 +8810,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>São Roque do Canaã</t>
+          <t>São Mateus</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3204955</v>
+        <v>3204906</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -9594,24 +8822,24 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>270.93</v>
+        <v>223.58</v>
       </c>
       <c r="F207" t="n">
-        <v>284.9</v>
+        <v>263.14</v>
       </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="n">
-        <v>240.12</v>
+        <v>214.84</v>
       </c>
       <c r="I207" t="n">
-        <v>279.35</v>
+        <v>261.49</v>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="L207" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="M207" t="inlineStr"/>
     </row>
@@ -9629,44 +8857,32 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>270.93</v>
+      </c>
+      <c r="F208" t="n">
+        <v>284.9</v>
       </c>
       <c r="G208" t="n">
         <v>297.41</v>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H208" t="n">
+        <v>240.12</v>
+      </c>
+      <c r="I208" t="n">
+        <v>279.35</v>
       </c>
       <c r="J208" t="n">
         <v>289.58</v>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K208" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L208" t="n">
+        <v>6</v>
       </c>
       <c r="M208" t="n">
         <v>5.1</v>
@@ -9678,44 +8894,38 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vargem Alta</t>
+          <t>São Roque do Canaã</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3205036</v>
+        <v>3204955</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>243.49</v>
+        <v>270.93</v>
       </c>
       <c r="F209" t="n">
-        <v>280.52</v>
-      </c>
-      <c r="G209" t="n">
-        <v>328.47</v>
-      </c>
+        <v>284.9</v>
+      </c>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="n">
-        <v>230.66</v>
+        <v>240.12</v>
       </c>
       <c r="I209" t="n">
-        <v>278.85</v>
-      </c>
-      <c r="J209" t="n">
-        <v>303.17</v>
-      </c>
+        <v>279.35</v>
+      </c>
+      <c r="J209" t="inlineStr"/>
       <c r="K209" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="L209" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M209" t="n">
-        <v>5.8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -9723,49 +8933,31 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Vargem Alta</t>
+          <t>São Roque do Canaã</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3205036</v>
+        <v>3204955</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" t="n">
-        <v>281.82</v>
-      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>328.47</v>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I210" t="n">
-        <v>281.41</v>
-      </c>
+        <v>297.41</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="n">
-        <v>303.17</v>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L210" t="n">
-        <v>6</v>
-      </c>
+        <v>289.58</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
       <c r="M210" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="211">
@@ -9782,30 +8974,36 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>243.49</v>
       </c>
       <c r="F211" t="n">
-        <v>278.61</v>
-      </c>
-      <c r="G211" t="inlineStr"/>
+        <v>280.52</v>
+      </c>
+      <c r="G211" t="n">
+        <v>328.47</v>
+      </c>
       <c r="H211" t="n">
         <v>230.66</v>
       </c>
       <c r="I211" t="n">
-        <v>275.07</v>
-      </c>
-      <c r="J211" t="inlineStr"/>
+        <v>278.85</v>
+      </c>
+      <c r="J211" t="n">
+        <v>303.17</v>
+      </c>
       <c r="K211" t="n">
         <v>6.7</v>
       </c>
       <c r="L211" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M211" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="M211" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -9813,50 +9011,38 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Venda Nova do Imigrante</t>
+          <t>Vargem Alta</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3205069</v>
+        <v>3205036</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>243.49</v>
       </c>
       <c r="F212" t="n">
-        <v>292.02</v>
-      </c>
-      <c r="G212" t="n">
-        <v>301.69</v>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>278.61</v>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="n">
+        <v>230.66</v>
       </c>
       <c r="I212" t="n">
-        <v>276.24</v>
-      </c>
-      <c r="J212" t="n">
-        <v>288.16</v>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>275.07</v>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="n">
+        <v>6.7</v>
       </c>
       <c r="L212" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M212" t="n">
-        <v>5.2</v>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9864,38 +9050,38 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Venda Nova do Imigrante</t>
+          <t>Vargem Alta</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3205069</v>
+        <v>3205036</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E213" t="n">
-        <v>254.57</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="n">
-        <v>273.6</v>
-      </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="n">
-        <v>241.48</v>
-      </c>
+        <v>281.82</v>
+      </c>
+      <c r="G213" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>270.2</v>
-      </c>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="n">
-        <v>7.2</v>
-      </c>
+        <v>281.41</v>
+      </c>
+      <c r="J213" t="n">
+        <v>303.17</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M213" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M213" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -9911,36 +9097,30 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E214" t="n">
         <v>254.57</v>
       </c>
       <c r="F214" t="n">
-        <v>285.23</v>
-      </c>
-      <c r="G214" t="n">
-        <v>315.4</v>
-      </c>
+        <v>273.6</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="n">
         <v>241.48</v>
       </c>
       <c r="I214" t="n">
-        <v>274.01</v>
-      </c>
-      <c r="J214" t="n">
-        <v>294.89</v>
-      </c>
+        <v>270.2</v>
+      </c>
+      <c r="J214" t="inlineStr"/>
       <c r="K214" t="n">
         <v>7.2</v>
       </c>
       <c r="L214" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M214" t="n">
-        <v>5.3</v>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -9948,49 +9128,43 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Viana</t>
+          <t>Venda Nova do Imigrante</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3205101</v>
+        <v>3205069</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>254.57</v>
       </c>
       <c r="F215" t="n">
-        <v>242.23</v>
+        <v>285.23</v>
       </c>
       <c r="G215" t="n">
-        <v>274.05</v>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>315.4</v>
+      </c>
+      <c r="H215" t="n">
+        <v>241.48</v>
       </c>
       <c r="I215" t="n">
-        <v>256.79</v>
+        <v>274.01</v>
       </c>
       <c r="J215" t="n">
-        <v>283</v>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>294.89</v>
+      </c>
+      <c r="K215" t="n">
+        <v>7.2</v>
       </c>
       <c r="L215" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="M215" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="216">
@@ -9999,38 +9173,38 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Viana</t>
+          <t>Venda Nova do Imigrante</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3205101</v>
+        <v>3205069</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E216" t="n">
-        <v>246.92</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>251.11</v>
-      </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="n">
-        <v>235.01</v>
-      </c>
+        <v>292.02</v>
+      </c>
+      <c r="G216" t="n">
+        <v>301.69</v>
+      </c>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
-        <v>255.33</v>
-      </c>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="n">
-        <v>6.9</v>
-      </c>
+        <v>276.24</v>
+      </c>
+      <c r="J216" t="n">
+        <v>288.16</v>
+      </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="n">
-        <v>5</v>
-      </c>
-      <c r="M216" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -10046,32 +9220,26 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E217" t="n">
-        <v>246.92</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>250.34</v>
+        <v>242.23</v>
       </c>
       <c r="G217" t="n">
         <v>274.05</v>
       </c>
-      <c r="H217" t="n">
-        <v>235.01</v>
-      </c>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>255.45</v>
+        <v>256.79</v>
       </c>
       <c r="J217" t="n">
         <v>283</v>
       </c>
-      <c r="K217" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="K217" t="inlineStr"/>
       <c r="L217" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M217" t="n">
         <v>4.6</v>
@@ -10083,44 +9251,38 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Vila Pavão</t>
+          <t>Viana</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3205150</v>
+        <v>3205101</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>239.67</v>
+        <v>246.92</v>
       </c>
       <c r="F218" t="n">
-        <v>284.24</v>
-      </c>
-      <c r="G218" t="n">
-        <v>323.72</v>
-      </c>
+        <v>251.11</v>
+      </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="n">
-        <v>229.44</v>
+        <v>235.01</v>
       </c>
       <c r="I218" t="n">
-        <v>275.62</v>
-      </c>
-      <c r="J218" t="n">
-        <v>301.46</v>
-      </c>
+        <v>255.33</v>
+      </c>
+      <c r="J218" t="inlineStr"/>
       <c r="K218" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="L218" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M218" t="n">
-        <v>5.3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10128,31 +9290,43 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Vila Pavão</t>
+          <t>Viana</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3205150</v>
+        <v>3205101</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>246.92</v>
+      </c>
+      <c r="F219" t="n">
+        <v>250.34</v>
+      </c>
       <c r="G219" t="n">
-        <v>323.72</v>
-      </c>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
+        <v>274.05</v>
+      </c>
+      <c r="H219" t="n">
+        <v>235.01</v>
+      </c>
+      <c r="I219" t="n">
+        <v>255.45</v>
+      </c>
       <c r="J219" t="n">
-        <v>301.46</v>
-      </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="K219" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L219" t="n">
+        <v>5</v>
+      </c>
       <c r="M219" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="220">
@@ -10169,30 +9343,24 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Municipal</t>
-        </is>
-      </c>
-      <c r="E220" t="n">
-        <v>239.67</v>
-      </c>
-      <c r="F220" t="n">
-        <v>284.24</v>
-      </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="n">
-        <v>229.44</v>
-      </c>
-      <c r="I220" t="n">
-        <v>275.62</v>
-      </c>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L220" t="n">
-        <v>6</v>
-      </c>
-      <c r="M220" t="inlineStr"/>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="n">
+        <v>301.46</v>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10200,44 +9368,38 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Vila Valério</t>
+          <t>Vila Pavão</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3205176</v>
+        <v>3205150</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Estadual</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>265.64</v>
+        <v>239.67</v>
       </c>
       <c r="F221" t="n">
-        <v>258.74</v>
-      </c>
-      <c r="G221" t="n">
-        <v>291.52</v>
-      </c>
+        <v>284.24</v>
+      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="n">
-        <v>249.72</v>
+        <v>229.44</v>
       </c>
       <c r="I221" t="n">
-        <v>262.43</v>
-      </c>
-      <c r="J221" t="n">
-        <v>292.18</v>
-      </c>
+        <v>275.62</v>
+      </c>
+      <c r="J221" t="inlineStr"/>
       <c r="K221" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="L221" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M221" t="n">
-        <v>4.9</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10245,38 +9407,44 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Vila Valério</t>
+          <t>Vila Pavão</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3205176</v>
+        <v>3205150</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>248.12</v>
+        <v>239.67</v>
       </c>
       <c r="F222" t="n">
-        <v>274.06</v>
-      </c>
-      <c r="G222" t="inlineStr"/>
+        <v>284.24</v>
+      </c>
+      <c r="G222" t="n">
+        <v>323.72</v>
+      </c>
       <c r="H222" t="n">
-        <v>220.69</v>
+        <v>229.44</v>
       </c>
       <c r="I222" t="n">
-        <v>260.53</v>
-      </c>
-      <c r="J222" t="inlineStr"/>
+        <v>275.62</v>
+      </c>
+      <c r="J222" t="n">
+        <v>301.46</v>
+      </c>
       <c r="K222" t="n">
         <v>6.7</v>
       </c>
       <c r="L222" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M222" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="M222" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10292,36 +9460,30 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>253.3</v>
+        <v>248.12</v>
       </c>
       <c r="F223" t="n">
-        <v>267.69</v>
-      </c>
-      <c r="G223" t="n">
-        <v>291.52</v>
-      </c>
+        <v>274.06</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="n">
-        <v>229.27</v>
+        <v>220.69</v>
       </c>
       <c r="I223" t="n">
-        <v>261.32</v>
-      </c>
-      <c r="J223" t="n">
-        <v>292.18</v>
-      </c>
+        <v>260.53</v>
+      </c>
+      <c r="J223" t="inlineStr"/>
       <c r="K223" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="L223" t="n">
         <v>5.4</v>
       </c>
-      <c r="M223" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10329,49 +9491,43 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Vila Velha</t>
+          <t>Vila Valério</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3205200</v>
+        <v>3205176</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E224" t="n">
+        <v>265.64</v>
       </c>
       <c r="F224" t="n">
-        <v>243.44</v>
+        <v>258.74</v>
       </c>
       <c r="G224" t="n">
-        <v>274.22</v>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>291.52</v>
+      </c>
+      <c r="H224" t="n">
+        <v>249.72</v>
       </c>
       <c r="I224" t="n">
-        <v>252.31</v>
+        <v>262.43</v>
       </c>
       <c r="J224" t="n">
-        <v>278.03</v>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>292.18</v>
+      </c>
+      <c r="K224" t="n">
+        <v>7.6</v>
       </c>
       <c r="L224" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M224" t="n">
         <v>4.9</v>
-      </c>
-      <c r="M224" t="n">
-        <v>4.7</v>
       </c>
     </row>
     <row r="225">
@@ -10380,38 +9536,44 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Vila Velha</t>
+          <t>Vila Valério</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>3205200</v>
+        <v>3205176</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>237.54</v>
+        <v>253.3</v>
       </c>
       <c r="F225" t="n">
-        <v>256.49</v>
-      </c>
-      <c r="G225" t="inlineStr"/>
+        <v>267.69</v>
+      </c>
+      <c r="G225" t="n">
+        <v>291.52</v>
+      </c>
       <c r="H225" t="n">
-        <v>228.24</v>
+        <v>229.27</v>
       </c>
       <c r="I225" t="n">
-        <v>259.95</v>
-      </c>
-      <c r="J225" t="inlineStr"/>
+        <v>261.32</v>
+      </c>
+      <c r="J225" t="n">
+        <v>292.18</v>
+      </c>
       <c r="K225" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="L225" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M225" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="M225" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10427,32 +9589,26 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E226" t="n">
-        <v>237.54</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="n">
-        <v>255.32</v>
+        <v>243.44</v>
       </c>
       <c r="G226" t="n">
-        <v>276.45</v>
-      </c>
-      <c r="H226" t="n">
-        <v>228.24</v>
-      </c>
+        <v>274.22</v>
+      </c>
+      <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>259.26</v>
+        <v>252.31</v>
       </c>
       <c r="J226" t="n">
-        <v>279.63</v>
-      </c>
-      <c r="K226" t="n">
-        <v>6.6</v>
-      </c>
+        <v>278.03</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="M226" t="n">
         <v>4.7</v>
@@ -10464,11 +9620,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vila Velha</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3205309</v>
+        <v>3205200</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -10476,24 +9632,24 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>234.15</v>
+        <v>237.54</v>
       </c>
       <c r="F227" t="n">
-        <v>264.84</v>
+        <v>256.49</v>
       </c>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="n">
-        <v>222.52</v>
+        <v>228.24</v>
       </c>
       <c r="I227" t="n">
-        <v>267.57</v>
+        <v>259.95</v>
       </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L227" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M227" t="inlineStr"/>
     </row>
@@ -10503,49 +9659,43 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vila Velha</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3205309</v>
+        <v>3205200</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>237.54</v>
       </c>
       <c r="F228" t="n">
-        <v>230.83</v>
+        <v>255.32</v>
       </c>
       <c r="G228" t="n">
-        <v>281.37</v>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>276.45</v>
+      </c>
+      <c r="H228" t="n">
+        <v>228.24</v>
       </c>
       <c r="I228" t="n">
-        <v>232.32</v>
+        <v>259.26</v>
       </c>
       <c r="J228" t="n">
-        <v>284.03</v>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>279.63</v>
+      </c>
+      <c r="K228" t="n">
+        <v>6.6</v>
       </c>
       <c r="L228" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="M228" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="229">
@@ -10599,49 +9749,37 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Água Doce do Norte</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3200169</v>
+        <v>3205309</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
           <t>Estadual</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="n">
-        <v>275.82</v>
+        <v>230.83</v>
       </c>
       <c r="G230" t="n">
-        <v>284</v>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>281.37</v>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>274.17</v>
+        <v>232.32</v>
       </c>
       <c r="J230" t="n">
-        <v>281.29</v>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>284.03</v>
+      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="M230" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="231">
@@ -10650,11 +9788,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Água Doce do Norte</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3200169</v>
+        <v>3205309</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -10662,24 +9800,24 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>239.08</v>
+        <v>234.15</v>
       </c>
       <c r="F231" t="n">
-        <v>251.04</v>
+        <v>264.84</v>
       </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="n">
-        <v>227.89</v>
+        <v>222.52</v>
       </c>
       <c r="I231" t="n">
-        <v>247.65</v>
+        <v>267.57</v>
       </c>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="L231" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="M231" t="inlineStr"/>
     </row>
@@ -10697,32 +9835,26 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E232" t="n">
-        <v>239.08</v>
-      </c>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="n">
-        <v>270.45</v>
+        <v>275.82</v>
       </c>
       <c r="G232" t="n">
         <v>284</v>
       </c>
-      <c r="H232" t="n">
-        <v>227.89</v>
-      </c>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>268.42</v>
+        <v>274.17</v>
       </c>
       <c r="J232" t="n">
         <v>281.29</v>
       </c>
-      <c r="K232" t="n">
-        <v>6.7</v>
-      </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="M232" t="n">
         <v>4.8</v>
@@ -10734,44 +9866,38 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Águia Branca</t>
+          <t>Água Doce do Norte</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3200136</v>
+        <v>3200169</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>283.23</v>
+        <v>239.08</v>
       </c>
       <c r="F233" t="n">
-        <v>271.23</v>
-      </c>
-      <c r="G233" t="n">
-        <v>279.37</v>
-      </c>
+        <v>251.04</v>
+      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="n">
-        <v>259.79</v>
+        <v>227.89</v>
       </c>
       <c r="I233" t="n">
-        <v>262.98</v>
-      </c>
-      <c r="J233" t="n">
-        <v>272.56</v>
-      </c>
+        <v>247.65</v>
+      </c>
+      <c r="J233" t="inlineStr"/>
       <c r="K233" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="L233" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M233" t="n">
-        <v>4.7</v>
-      </c>
+        <v>4.9</v>
+      </c>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10779,37 +9905,43 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Águia Branca</t>
+          <t>Água Doce do Norte</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3200136</v>
+        <v>3200169</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Estadual</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr"/>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>239.08</v>
+      </c>
       <c r="F234" t="n">
-        <v>263.25</v>
+        <v>270.45</v>
       </c>
       <c r="G234" t="n">
-        <v>279.37</v>
-      </c>
-      <c r="H234" t="inlineStr"/>
+        <v>284</v>
+      </c>
+      <c r="H234" t="n">
+        <v>227.89</v>
+      </c>
       <c r="I234" t="n">
-        <v>266.66</v>
+        <v>268.42</v>
       </c>
       <c r="J234" t="n">
-        <v>272.56</v>
-      </c>
-      <c r="K234" t="inlineStr"/>
+        <v>281.29</v>
+      </c>
+      <c r="K234" t="n">
+        <v>6.7</v>
+      </c>
       <c r="L234" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M234" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="235">
@@ -10826,30 +9958,114 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E235" t="n">
         <v>283.23</v>
       </c>
       <c r="F235" t="n">
-        <v>295.16</v>
-      </c>
-      <c r="G235" t="inlineStr"/>
+        <v>271.23</v>
+      </c>
+      <c r="G235" t="n">
+        <v>279.37</v>
+      </c>
       <c r="H235" t="n">
         <v>259.79</v>
       </c>
       <c r="I235" t="n">
-        <v>251.95</v>
-      </c>
-      <c r="J235" t="inlineStr"/>
+        <v>262.98</v>
+      </c>
+      <c r="J235" t="n">
+        <v>272.56</v>
+      </c>
       <c r="K235" t="n">
         <v>8.1</v>
       </c>
       <c r="L235" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M235" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Águia Branca</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>3200136</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="G236" t="n">
+        <v>279.37</v>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="n">
+        <v>266.66</v>
+      </c>
+      <c r="J236" t="n">
+        <v>272.56</v>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M236" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Águia Branca</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>3200136</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>283.23</v>
+      </c>
+      <c r="F237" t="n">
+        <v>295.16</v>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>259.79</v>
+      </c>
+      <c r="I237" t="n">
+        <v>251.95</v>
+      </c>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L237" t="n">
         <v>5.7</v>
       </c>
-      <c r="M235" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
